--- a/assets/templates/mof_r5.xlsx
+++ b/assets/templates/mof_r5.xlsx
@@ -608,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -819,6 +819,45 @@
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1240,13 +1279,13 @@
       <c r="B12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="2"/>
       <c r="F12" s="17"/>
       <c r="G12" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="100"/>
       <c r="I12" s="2"/>
       <c r="K12" s="17"/>
     </row>
@@ -1254,13 +1293,13 @@
       <c r="B13" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="4"/>
       <c r="F13" s="17"/>
       <c r="G13" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="101"/>
       <c r="I13" s="4"/>
       <c r="K13" s="17"/>
     </row>
@@ -1268,90 +1307,91 @@
       <c r="B14" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="4"/>
       <c r="E14" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="19"/>
+      <c r="F14" s="102"/>
       <c r="G14" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="101"/>
       <c r="I14" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="2"/>
+      <c r="J14" s="100"/>
       <c r="K14" s="17"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="4"/>
       <c r="E15" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="17"/>
+      <c r="F15" s="103"/>
       <c r="G15" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="4"/>
+      <c r="H15" s="101"/>
       <c r="I15" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="4"/>
+      <c r="J15" s="101"/>
       <c r="K15" s="17"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>21</v>
       </c>
+      <c r="C16" s="104"/>
       <c r="D16" s="4"/>
       <c r="E16" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="34"/>
+      <c r="F16" s="105"/>
       <c r="G16" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="101"/>
       <c r="I16" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="4"/>
+      <c r="J16" s="101"/>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B17" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="100"/>
       <c r="E17" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="35"/>
+      <c r="F17" s="106"/>
       <c r="G17" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="4"/>
+      <c r="H17" s="101"/>
       <c r="I17" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="13"/>
+      <c r="J17" s="107"/>
       <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B18" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="33"/>
+      <c r="C18" s="108"/>
       <c r="F18" s="17"/>
       <c r="G18" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="36"/>
+      <c r="H18" s="109"/>
       <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1359,32 +1399,32 @@
         <v>27</v>
       </c>
       <c r="C19" s="79"/>
-      <c r="D19" s="2"/>
+      <c r="D19" s="100"/>
       <c r="E19" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="19"/>
+      <c r="F19" s="102"/>
       <c r="G19" s="50" t="s">
         <v>27</v>
       </c>
       <c r="H19" s="50"/>
-      <c r="I19" s="2"/>
+      <c r="I19" s="100"/>
       <c r="J19" t="s">
         <v>28</v>
       </c>
-      <c r="K19" s="19"/>
+      <c r="K19" s="102"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B20" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="39"/>
+      <c r="E20" s="110"/>
       <c r="F20" s="19"/>
       <c r="G20" t="s">
         <v>29</v>
       </c>
       <c r="I20" s="40"/>
-      <c r="K20" s="41"/>
+      <c r="K20" s="111"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="83" t="s">
@@ -1425,10 +1465,12 @@
       <c r="B23" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="C23" s="104"/>
       <c r="F23" s="17"/>
       <c r="G23" t="s">
         <v>34</v>
       </c>
+      <c r="H23" s="104"/>
       <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -1938,7 +1980,7 @@
       <c r="H54" t="s">
         <v>69</v>
       </c>
-      <c r="I54" s="50"/>
+      <c r="I54" s="112"/>
       <c r="J54" s="50"/>
       <c r="K54" s="17"/>
     </row>
